--- a/output/tables/results.xlsx
+++ b/output/tables/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB66"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,120 +451,135 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>prefactor_mode</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sigma_mode</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>software_version</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>absorption_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>light_source_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>absorbed_flux_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>reference_concentration_molar</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>reference_path_cm</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>light_flux_total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>td_method_basis</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>td_solvent</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>gaussian_lambda_max_nm</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>gaussian_molar_absorptivity_max</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>gaussian_absorptance_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>gaussian_absorbed_flux</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>gaussian_absorbed_fraction</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>gaussian_shape_overlap</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>lorentzian_lambda_max_nm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>lorentzian_molar_absorptivity_max</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>lorentzian_absorptance_max</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>lorentzian_absorbed_flux</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>lorentzian_absorbed_fraction</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>lorentzian_shape_overlap</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>delta_absorbed_flux</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>delta_absorbed_fraction</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>delta_shape_overlap</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>abs_delta_absorbed_fraction</t>
         </is>
@@ -591,80 +606,95 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>589.120214277655</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>541.7341734173417</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>32988.58201387445</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>0.5321418708397718</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>195.1641202244114</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0.3312806376262446</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>0.7173293031215805</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>547.9147914791479</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>23651.10743606742</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>0.4199186195425911</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>167.740142678494</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>0.2847299050570982</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>0.8079591779275814</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>27.42397754591735</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>0.04655073256914644</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>-0.09062987480600093</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>0.04655073256914644</v>
       </c>
     </row>
@@ -689,80 +719,95 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>3074.773478417718</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>541.7341734173417</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>32988.58201387445</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>0.5321418708397718</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>1232.285141467841</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0.4007726585771049</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>0.9663996933215354</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>547.9147914791479</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>23651.10743606742</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>0.4199186195425911</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>1009.352879450743</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>0.3282690209654588</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>0.9802476217996446</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>222.9322620170989</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>0.07250363761164613</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>-0.01384792847810923</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>0.07250363761164613</v>
       </c>
     </row>
@@ -787,80 +832,95 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>3185.413367312932</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>541.7341734173417</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>32988.58201387445</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>0.5321418708397718</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>1317.792961216862</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0.4136960605299687</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>0.943916076115075</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>547.9147914791479</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>23651.10743606742</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>0.4199186195425911</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>1079.299658983204</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>0.3388256199520037</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>0.9582037226186065</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>238.4933022336579</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>0.07487044057796494</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>-0.01428764650353154</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>0.07487044057796494</v>
       </c>
     </row>
@@ -885,80 +945,95 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>3155.042987823557</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>541.7341734173417</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>32988.58201387445</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>0.5321418708397718</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>1300.296335945985</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>0.4121326843926675</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>0.9514098832820012</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>547.9147914791479</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>23651.10743606742</v>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
         <v>0.4199186195425911</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
         <v>1060.548515940135</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>0.3361439194436247</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>0.9623919461404857</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>239.7478200058499</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>0.07598876494904278</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>-0.01098206285848458</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>0.07598876494904278</v>
       </c>
     </row>
@@ -983,80 +1058,95 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>3131.547799407255</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>541.7341734173417</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>32988.58201387445</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>0.5321418708397718</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>1278.081073131293</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>0.4081307886704493</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>0.9374167216088671</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>547.9147914791479</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>23651.10743606742</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>0.4199186195425911</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>1042.619954383493</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>0.3329407759897015</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>0.9485505689926109</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>235.4611187477994</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>0.07519001268074788</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>-0.01113384738374379</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>0.07519001268074788</v>
       </c>
     </row>
@@ -1081,80 +1171,95 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>589.120214277655</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>551.3351335133514</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>16569.6386908676</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>0.3171841195240284</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>99.54478410385921</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>0.1689719376306163</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>0.6037617831939711</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>552.8952895289528</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>11997.34021763766</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>0.2413759654111365</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>86.16586612661089</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>0.1462619411765771</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>0.7180561231744245</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>13.37891797724832</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>0.02270999645403915</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>-0.1142943399804534</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>0.02270999645403915</v>
       </c>
     </row>
@@ -1179,80 +1284,95 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>3074.773478417718</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>551.3351335133514</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>16569.6386908676</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>0.3171841195240284</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>675.5605571725962</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>0.219710675246308</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>0.9438503974432021</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>552.8952895289528</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>11997.34021763766</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>0.2413759654111365</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>536.4858672950521</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>0.1744798018653161</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>0.9695617184453854</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>139.0746898775441</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
         <v>0.04523087338099196</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AD8" t="n">
         <v>-0.02571132100218332</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>0.04523087338099196</v>
       </c>
     </row>
@@ -1277,80 +1397,95 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>3185.413367312932</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>551.3351335133514</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>16569.6386908676</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>0.3171841195240284</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>738.2268801173557</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>0.2317523018182378</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>0.918451196524779</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>552.8952895289528</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>11997.34021763766</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>0.2413759654111365</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>584.1358785271857</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>0.1833783597825283</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>0.9374892832238393</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>154.09100159017</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>0.04837394203570949</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
         <v>-0.01903808669906026</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>0.04837394203570949</v>
       </c>
     </row>
@@ -1375,80 +1510,95 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>3155.042987823557</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>551.3351335133514</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>16569.6386908676</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>0.3171841195240284</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>718.6323300609674</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>0.2277725954398807</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>0.9162088752936258</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>552.8952895289528</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>11997.34021763766</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>0.2413759654111365</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>567.4014546820595</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>0.1798395320988859</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>0.9382442815905292</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>151.230875378908</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>0.04793306334099476</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
         <v>-0.02203540629690337</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AE10" t="n">
         <v>0.04793306334099476</v>
       </c>
     </row>
@@ -1473,80 +1623,95 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>3131.547799407255</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>551.3351335133514</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>16569.6386908676</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>0.3171841195240284</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>698.6574810865748</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>0.2231029273188223</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>0.8887820385615305</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>552.8952895289528</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>11997.34021763766</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>0.2413759654111365</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>554.137584209921</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>0.1769532575280534</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>0.9172484302992833</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>144.5198968766538</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>0.0461496697907689</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>-0.02846639173775278</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>0.0461496697907689</v>
       </c>
     </row>
@@ -1571,80 +1736,95 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>589.120214277655</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>531.8331833183317</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>25704.33610506488</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>0.4467051358894837</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>148.2014965036682</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>0.2515641000120565</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>0.6437253268490498</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>536.8136813681368</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>18438.1078984617</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>0.3459379954903001</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>129.2048399869512</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>0.2193182933730676</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>0.7572106837295302</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>18.996656516717</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>0.03224580663898893</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
         <v>-0.1134853568804803</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
         <v>0.03224580663898893</v>
       </c>
     </row>
@@ -1669,80 +1849,95 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>3074.773478417718</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>531.8331833183317</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>25704.33610506488</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>0.4467051358894837</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>1011.825289968817</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>0.3290731161404133</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>0.9724484854323434</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>536.8136813681368</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>18438.1078984617</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>0.3459379954903001</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>809.6378833165371</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>0.2633162699624876</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>0.9798577108144662</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>202.1874066522795</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>0.06575684617792571</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AD13" t="n">
         <v>-0.007409225382122742</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AE13" t="n">
         <v>0.06575684617792571</v>
       </c>
     </row>
@@ -1767,80 +1962,95 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>3185.413367312932</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>531.8331833183317</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>25704.33610506488</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>0.4467051358894837</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>1014.114798047158</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>0.3183620714515361</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>0.887048930307912</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>536.8136813681368</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>18438.1078984617</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>0.3459379954903001</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>826.1952557672307</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
         <v>0.2593683018490536</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>0.9139590424256103</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>187.9195422799269</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
         <v>0.05899376960248248</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AD14" t="n">
         <v>-0.02691011211769834</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AE14" t="n">
         <v>0.05899376960248248</v>
       </c>
     </row>
@@ -1865,80 +2075,95 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>3155.042987823557</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>531.8331833183317</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>25704.33610506488</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>0.4467051358894837</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>1034.668446477948</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>0.3279411565772969</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>0.9333186247085664</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>536.8136813681368</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>18438.1078984617</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>0.3459379954903001</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>831.9000920409798</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>0.2636731401922511</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>0.9492207094019836</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>202.768354436968</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AC15" t="n">
         <v>0.06426801638504576</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
         <v>-0.01590208469341714</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AE15" t="n">
         <v>0.06426801638504576</v>
       </c>
     </row>
@@ -1963,80 +2188,95 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="K16" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>3131.547799407255</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>531.8331833183317</v>
       </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
         <v>25704.33610506488</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>0.4467051358894837</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>1033.179650699566</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>0.3299261952492401</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>0.9535649444074964</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>536.8136813681368</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>18438.1078984617</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>0.3459379954903001</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>827.9729358776634</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>0.2643973488236021</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>0.9590761867938732</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>205.2067148219027</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
         <v>0.06552884642563805</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
         <v>-0.005511242386376791</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="n">
         <v>0.06552884642563805</v>
       </c>
     </row>
@@ -2061,80 +2301,95 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
         <v>589.120214277655</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>682.2682268226822</v>
       </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>16066.97570356259</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>0.3092351295580885</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>131.3829337520858</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>0.2230154908420177</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>0.7952110296884214</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>683.5883588358836</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>11851.44322102127</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>0.2388231563807234</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>102.3833982557403</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>0.1737903330668714</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>0.8299042955948821</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>28.9995354963455</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>0.04922515777514622</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
         <v>-0.03469326590646071</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
         <v>0.04922515777514622</v>
       </c>
     </row>
@@ -2159,80 +2414,95 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>3074.773478417718</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>682.2682268226822</v>
       </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>16066.97570356259</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>0.3092351295580885</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>685.6480938046921</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>0.2229914166416992</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>0.985237048937642</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>683.5883588358836</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>11851.44322102127</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>0.2388231563807234</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>528.413620809494</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>0.1718544876617761</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>0.9850963245818783</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>157.2344729951981</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
         <v>0.05113692897992314</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
         <v>0.0001407243557636217</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AE18" t="n">
         <v>0.05113692897992314</v>
       </c>
     </row>
@@ -2257,80 +2527,95 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="M19" t="n">
         <v>3185.413367312932</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>682.2682268226822</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>16066.97570356259</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>0.3092351295580885</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>801.4034579677772</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>0.2515853880037567</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>0.950305902253067</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>683.5883588358836</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>11851.44322102127</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>0.2388231563807234</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>608.3470064254684</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>0.1909789833457759</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>0.9340587298547331</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>193.0564515423088</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
         <v>0.06060640465798081</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AD19" t="n">
         <v>0.01624717239833384</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AE19" t="n">
         <v>0.06060640465798081</v>
       </c>
     </row>
@@ -2355,80 +2640,95 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
+      <c r="M20" t="n">
         <v>3155.042987823557</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>682.2682268226822</v>
       </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
         <v>16066.97570356259</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>0.3092351295580885</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>757.7033994347767</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>0.240156283879182</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>0.9492295600449867</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>683.5883588358836</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>11851.44322102127</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>0.2388231563807234</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>579.1646081246234</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>0.1835678976038765</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>0.9392845159994535</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>178.5387913101532</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
         <v>0.05658838627530544</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
         <v>0.009945044045533202</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AE20" t="n">
         <v>0.05658838627530544</v>
       </c>
     </row>
@@ -2453,80 +2753,95 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>3131.547799407255</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>682.2682268226822</v>
       </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
         <v>16066.97570356259</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>0.3092351295580885</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>733.1575881424905</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>0.234119877806516</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>0.9643111906963994</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>683.5883588358836</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>11851.44322102127</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>0.2388231563807234</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>562.2065064201043</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>0.1795299137782664</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>0.9679241527672445</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>170.9510817223861</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AC21" t="n">
         <v>0.05458996402824956</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
         <v>-0.00361296207084516</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AE21" t="n">
         <v>0.05458996402824956</v>
       </c>
     </row>
@@ -2551,80 +2866,95 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="K22" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
         <v>589.120214277655</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>800</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>31238.80564063707</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
         <v>0.5129069380768544</v>
       </c>
-      <c r="P22" t="n">
+      <c r="S22" t="n">
         <v>159.6831808152138</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
         <v>0.2710536439680788</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>0.5846119979005773</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>800</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>21810.56039922252</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>0.3948063033569803</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>134.2045698287411</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>0.2278050669052241</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>0.6618446224990249</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>25.47861098647266</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
         <v>0.04324857706285473</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AD22" t="n">
         <v>-0.0772326245984476</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AE22" t="n">
         <v>0.04324857706285473</v>
       </c>
     </row>
@@ -2649,80 +2979,95 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="K23" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="M23" t="n">
         <v>3074.773478417718</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>800</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
         <v>31238.80564063707</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
         <v>0.5129069380768544</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>723.723433981091</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>0.2353745532999458</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>0.8774914774418061</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>800</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>21810.56039922252</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>0.3948063033569803</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>651.7465140573661</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>0.2119657004433236</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>0.9504424951709146</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>71.97691992372495</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
         <v>0.02340885285662225</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AD23" t="n">
         <v>-0.0729510177291085</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AE23" t="n">
         <v>0.02340885285662225</v>
       </c>
     </row>
@@ -2747,80 +3092,95 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="K24" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I24" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="M24" t="n">
         <v>3185.413367312932</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>800</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>31238.80564063707</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
         <v>0.5129069380768544</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>995.3014382549862</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>0.3124559746211453</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>0.7971337885571808</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>800</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>21810.56039922252</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>0.3948063033569803</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>829.5203101693506</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>0.2604121394985844</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>0.881500527080207</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>165.7811280856356</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AC24" t="n">
         <v>0.05204383512256089</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AD24" t="n">
         <v>-0.08436673852302623</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AE24" t="n">
         <v>0.05204383512256089</v>
       </c>
     </row>
@@ -2845,80 +3205,95 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="K25" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I25" t="n">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
         <v>3155.042987823557</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>800</v>
       </c>
-      <c r="N25" t="n">
+      <c r="Q25" t="n">
         <v>31238.80564063707</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
         <v>0.5129069380768544</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>865.1001431827123</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="T25" t="n">
         <v>0.274195992422748</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>0.7152817275307217</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>800</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>21810.56039922252</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>0.3948063033569803</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>745.6257293109262</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>0.236328231402413</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>0.8248141524003904</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>119.4744138717861</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>0.03786776102033498</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AD25" t="n">
         <v>-0.1095324248696686</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AE25" t="n">
         <v>0.03786776102033498</v>
       </c>
     </row>
@@ -2943,80 +3318,95 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>absorptance (Beer-Lambert at c=1e-05 M, L=1 cm)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="K26" t="n">
         <v>1e-05</v>
       </c>
-      <c r="I26" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
+      <c r="M26" t="n">
         <v>3131.547799407255</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>b3lyp/6-31g</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>800</v>
       </c>
-      <c r="N26" t="n">
+      <c r="Q26" t="n">
         <v>31238.80564063707</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
         <v>0.5129069380768544</v>
       </c>
-      <c r="P26" t="n">
+      <c r="S26" t="n">
         <v>797.7301729338531</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="T26" t="n">
         <v>0.2547398998938636</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>0.7772674381000193</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>800</v>
       </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
         <v>21810.56039922252</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>0.3948063033569803</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>702.0669399960465</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
         <v>0.2241916729257446</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>0.8622745743622758</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>95.66323293780658</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AC26" t="n">
         <v>0.03054822696811907</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AD26" t="n">
         <v>-0.08500713626225653</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="n">
         <v>0.03054822696811907</v>
       </c>
     </row>
@@ -3041,76 +3431,91 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>376</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="P27" t="n">
+      <c r="S27" t="n">
         <v>14.64143850148696</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="T27" t="n">
         <v>0.03076417399056257</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>0.1044749691709634</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>376</v>
       </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>14.64143850148696</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>0.03076417399056257</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>0.1044749691709634</v>
       </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
       <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3135,76 +3540,91 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>376</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="P28" t="n">
+      <c r="S28" t="n">
         <v>11.65408375693809</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="T28" t="n">
         <v>0.003873317114847875</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>0.03942717589370072</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>376</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>11.65408375693809</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
         <v>0.003873317114847875</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>0.03942717589370072</v>
       </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
       <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3229,76 +3649,91 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>376</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="P29" t="n">
+      <c r="S29" t="n">
         <v>0.4322675704048498</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="T29" t="n">
         <v>0.0001423098486237755</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>0.001654090102952419</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>376</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
         <v>0.4322675704048498</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Z29" t="n">
         <v>0.0001423098486237755</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AA29" t="n">
         <v>0.001654090102952419</v>
       </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
       <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3323,76 +3758,91 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>376</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
         <v>0.5084284760832409</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="T30" t="n">
         <v>0.0001659415177901094</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>0.00255062932607473</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>376</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
         <v>0.5084284760832409</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Z30" t="n">
         <v>0.0001659415177901094</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>0.00255062932607473</v>
       </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
       <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3417,76 +3867,91 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>376</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="P31" t="n">
+      <c r="S31" t="n">
         <v>0.405198199451443</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="T31" t="n">
         <v>0.0001332112681409803</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>0.00274323496549957</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>376</v>
       </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.4160710597008233</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
         <v>0.405198199451443</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
         <v>0.0001332112681409803</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AA31" t="n">
         <v>0.00274323496549957</v>
       </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
       <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3511,76 +3976,91 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>456</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>75.82550360493576</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="T32" t="n">
         <v>0.1593223907328072</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>0.2651767781496991</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>456</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
         <v>75.82550360493576</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
         <v>0.1593223907328072</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AA32" t="n">
         <v>0.2651767781496991</v>
       </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
       <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3605,76 +4085,91 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>456</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>543.0902533582371</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
         <v>0.1804998845994397</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>0.3619273110167726</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>456</v>
       </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
         <v>543.0902533582371</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Z33" t="n">
         <v>0.1804998845994397</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AA33" t="n">
         <v>0.3619273110167726</v>
       </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
       <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3699,76 +4194,91 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>456</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="P34" t="n">
+      <c r="S34" t="n">
         <v>244.4411909225536</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
         <v>0.08047420454193234</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
         <v>0.1352329472580635</v>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
         <v>456</v>
       </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="V34" t="n">
+      <c r="Y34" t="n">
         <v>244.4411909225536</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Z34" t="n">
         <v>0.08047420454193234</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AA34" t="n">
         <v>0.1352329472580635</v>
       </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
       <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3793,76 +4303,91 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>456</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="P35" t="n">
+      <c r="S35" t="n">
         <v>404.2316113651386</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="T35" t="n">
         <v>0.1319336156098591</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
         <v>0.2121194433744345</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
         <v>456</v>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
         <v>404.2316113651386</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Z35" t="n">
         <v>0.1319336156098591</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AA35" t="n">
         <v>0.2121194433744345</v>
       </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
       <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3887,76 +4412,91 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>456</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
         <v>530.2313734481843</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="T36" t="n">
         <v>0.1743166523464046</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
         <v>0.2754992113554613</v>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
         <v>456</v>
       </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>0.7114042042645803</v>
       </c>
-      <c r="V36" t="n">
+      <c r="Y36" t="n">
         <v>530.2313734481843</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Z36" t="n">
         <v>0.1743166523464046</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AA36" t="n">
         <v>0.2754992113554613</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
       <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3981,76 +4521,91 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>436</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="P37" t="n">
+      <c r="S37" t="n">
         <v>47.80958073548521</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="T37" t="n">
         <v>0.1004561307287491</v>
       </c>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
         <v>0.1902295938643521</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>436</v>
       </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="V37" t="n">
+      <c r="Y37" t="n">
         <v>47.80958073548521</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Z37" t="n">
         <v>0.1004561307287491</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AA37" t="n">
         <v>0.1902295938643521</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
       <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4075,76 +4630,91 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
         <v>436</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="P38" t="n">
+      <c r="S38" t="n">
         <v>355.143786355461</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="T38" t="n">
         <v>0.1180345477698795</v>
       </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
         <v>0.2555015221859674</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>436</v>
       </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
         <v>355.143786355461</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Z38" t="n">
         <v>0.1180345477698795</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AA38" t="n">
         <v>0.2555015221859674</v>
       </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
       <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4169,76 +4739,91 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
         <v>436</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="P39" t="n">
+      <c r="S39" t="n">
         <v>124.5283833339041</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="T39" t="n">
         <v>0.040996865355904</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
         <v>0.09073802324688933</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>436</v>
       </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="V39" t="n">
+      <c r="Y39" t="n">
         <v>124.5283833339041</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
         <v>0.040996865355904</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AA39" t="n">
         <v>0.09073802324688933</v>
       </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
       <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4263,76 +4848,91 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
         <v>436</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="P40" t="n">
+      <c r="S40" t="n">
         <v>242.2886767082422</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
         <v>0.07907847936853221</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
         <v>0.142139376421505</v>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
         <v>436</v>
       </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="V40" t="n">
+      <c r="Y40" t="n">
         <v>242.2886767082422</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Z40" t="n">
         <v>0.07907847936853221</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AA40" t="n">
         <v>0.142139376421505</v>
       </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
       <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4357,76 +4957,91 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
         <v>436</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S41" t="n">
         <v>314.0736340365638</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="T41" t="n">
         <v>0.1032535365070656</v>
       </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
         <v>0.1801887944233585</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>436</v>
       </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
         <v>0.6574373575592655</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Y41" t="n">
         <v>314.0736340365638</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Z41" t="n">
         <v>0.1032535365070656</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AA41" t="n">
         <v>0.1801887944233585</v>
       </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
       <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4451,76 +5066,91 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>524</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="P42" t="n">
+      <c r="S42" t="n">
         <v>85.9346258352933</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="T42" t="n">
         <v>0.1805633907312021</v>
       </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
         <v>0.2249523059381396</v>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
         <v>524</v>
       </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="V42" t="n">
+      <c r="Y42" t="n">
         <v>85.9346258352933</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Z42" t="n">
         <v>0.1805633907312021</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AA42" t="n">
         <v>0.2249523059381396</v>
       </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
       <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4545,76 +5175,91 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="n">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
         <v>524</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="P43" t="n">
+      <c r="S43" t="n">
         <v>553.2842659534258</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="T43" t="n">
         <v>0.1838879367429994</v>
       </c>
-      <c r="R43" t="n">
+      <c r="U43" t="n">
         <v>0.5221730269476736</v>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
         <v>524</v>
       </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="V43" t="n">
+      <c r="Y43" t="n">
         <v>553.2842659534258</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Z43" t="n">
         <v>0.1838879367429994</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AA43" t="n">
         <v>0.5221730269476736</v>
       </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
       <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4639,76 +5284,91 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="n">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
         <v>524</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="P44" t="n">
+      <c r="S44" t="n">
         <v>426.5157596763167</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="T44" t="n">
         <v>0.1404162545396218</v>
       </c>
-      <c r="R44" t="n">
+      <c r="U44" t="n">
         <v>0.2219683883876972</v>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
         <v>524</v>
       </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="V44" t="n">
+      <c r="Y44" t="n">
         <v>426.5157596763167</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Z44" t="n">
         <v>0.1404162545396218</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AA44" t="n">
         <v>0.2219683883876972</v>
       </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
       <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4733,76 +5393,91 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="n">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
         <v>524</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="P45" t="n">
+      <c r="S45" t="n">
         <v>556.2256945259408</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="T45" t="n">
         <v>0.181541633337588</v>
       </c>
-      <c r="R45" t="n">
+      <c r="U45" t="n">
         <v>0.2708225500957613</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>524</v>
       </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="V45" t="n">
+      <c r="Y45" t="n">
         <v>556.2256945259408</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Z45" t="n">
         <v>0.181541633337588</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AA45" t="n">
         <v>0.2708225500957613</v>
       </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
       <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4827,76 +5502,91 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="n">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
         <v>524</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="P46" t="n">
+      <c r="S46" t="n">
         <v>574.1321960545034</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="T46" t="n">
         <v>0.1887493034779672</v>
       </c>
-      <c r="R46" t="n">
+      <c r="U46" t="n">
         <v>0.2846748853331426</v>
       </c>
-      <c r="S46" t="n">
+      <c r="V46" t="n">
         <v>524</v>
       </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
         <v>0.9236076271515453</v>
       </c>
-      <c r="V46" t="n">
+      <c r="Y46" t="n">
         <v>574.1321960545034</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Z46" t="n">
         <v>0.1887493034779672</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AA46" t="n">
         <v>0.2846748853331426</v>
       </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
       <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4921,76 +5611,91 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="n">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
         <v>224</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="P47" t="n">
+      <c r="S47" t="n">
         <v>131.9977400692832</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="T47" t="n">
         <v>0.277349895738733</v>
       </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
         <v>0.3535070820671439</v>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
         <v>224</v>
       </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="V47" t="n">
+      <c r="Y47" t="n">
         <v>131.9977400692832</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Z47" t="n">
         <v>0.277349895738733</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AA47" t="n">
         <v>0.3535070820671439</v>
       </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
       <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5015,76 +5720,91 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
         <v>224</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="P48" t="n">
+      <c r="S48" t="n">
         <v>814.126783869841</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="T48" t="n">
         <v>0.2705807913678156</v>
       </c>
-      <c r="R48" t="n">
+      <c r="U48" t="n">
         <v>0.3554126860997563</v>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
         <v>224</v>
       </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Y48" t="n">
         <v>814.126783869841</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Z48" t="n">
         <v>0.2705807913678156</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AA48" t="n">
         <v>0.3554126860997563</v>
       </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
       <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5109,76 +5829,91 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="n">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
         <v>224</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="P49" t="n">
+      <c r="S49" t="n">
         <v>431.0538398639197</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="T49" t="n">
         <v>0.141910267851644</v>
       </c>
-      <c r="R49" t="n">
+      <c r="U49" t="n">
         <v>0.1889057397347102</v>
       </c>
-      <c r="S49" t="n">
+      <c r="V49" t="n">
         <v>224</v>
       </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Y49" t="n">
         <v>431.0538398639197</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Z49" t="n">
         <v>0.141910267851644</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AA49" t="n">
         <v>0.1889057397347102</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
       <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5203,76 +5938,91 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="n">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
         <v>224</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="P50" t="n">
+      <c r="S50" t="n">
         <v>677.2092943944715</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="T50" t="n">
         <v>0.2210284109951957</v>
       </c>
-      <c r="R50" t="n">
+      <c r="U50" t="n">
         <v>0.27928166147006</v>
       </c>
-      <c r="S50" t="n">
+      <c r="V50" t="n">
         <v>224</v>
       </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="V50" t="n">
+      <c r="Y50" t="n">
         <v>677.2092943944715</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Z50" t="n">
         <v>0.2210284109951957</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AA50" t="n">
         <v>0.27928166147006</v>
       </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
       <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5297,76 +6047,91 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="n">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
         <v>224</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="P51" t="n">
+      <c r="S51" t="n">
         <v>783.9255466060235</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="T51" t="n">
         <v>0.2577200894102533</v>
       </c>
-      <c r="R51" t="n">
+      <c r="U51" t="n">
         <v>0.3267324444201085</v>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
         <v>224</v>
       </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
         <v>0.9998942695696258</v>
       </c>
-      <c r="V51" t="n">
+      <c r="Y51" t="n">
         <v>783.9255466060235</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Z51" t="n">
         <v>0.2577200894102533</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AA51" t="n">
         <v>0.3267324444201085</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
       <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5391,76 +6156,91 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="n">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
         <v>241</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="P52" t="n">
+      <c r="S52" t="n">
         <v>6.471192430580373</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="T52" t="n">
         <v>0.01359708541210399</v>
       </c>
-      <c r="R52" t="n">
+      <c r="U52" t="n">
         <v>0.02933167152328171</v>
       </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
         <v>241</v>
       </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="V52" t="n">
+      <c r="Y52" t="n">
         <v>6.471192430580373</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Z52" t="n">
         <v>0.01359708541210399</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AA52" t="n">
         <v>0.02933167152328171</v>
       </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
       <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5485,76 +6265,91 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
         <v>241</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="P53" t="n">
+      <c r="S53" t="n">
         <v>16.42743222906119</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="T53" t="n">
         <v>0.00545977322051988</v>
       </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
         <v>0.09973258780837142</v>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
         <v>241</v>
       </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="V53" t="n">
+      <c r="Y53" t="n">
         <v>16.42743222906119</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Z53" t="n">
         <v>0.00545977322051988</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AA53" t="n">
         <v>0.09973258780837142</v>
       </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
       <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5579,76 +6374,91 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
         <v>241</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="P54" t="n">
+      <c r="S54" t="n">
         <v>15.9957105341183</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="T54" t="n">
         <v>0.005266060423196087</v>
       </c>
-      <c r="R54" t="n">
+      <c r="U54" t="n">
         <v>0.01215127294039933</v>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
         <v>241</v>
       </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="V54" t="n">
+      <c r="Y54" t="n">
         <v>15.9957105341183</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Z54" t="n">
         <v>0.005266060423196087</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AA54" t="n">
         <v>0.01215127294039933</v>
       </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
       <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5673,76 +6483,91 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
         <v>241</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="P55" t="n">
+      <c r="S55" t="n">
         <v>16.15255200101371</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="T55" t="n">
         <v>0.005271889993024399</v>
       </c>
-      <c r="R55" t="n">
+      <c r="U55" t="n">
         <v>0.012468153771382</v>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
         <v>241</v>
       </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="V55" t="n">
+      <c r="Y55" t="n">
         <v>16.15255200101371</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Z55" t="n">
         <v>0.005271889993024399</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AA55" t="n">
         <v>0.012468153771382</v>
       </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
       <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5767,76 +6592,91 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
         <v>241</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="P56" t="n">
+      <c r="S56" t="n">
         <v>15.99925322594204</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="T56" t="n">
         <v>0.005259847685457967</v>
       </c>
-      <c r="R56" t="n">
+      <c r="U56" t="n">
         <v>0.01658264351099755</v>
       </c>
-      <c r="S56" t="n">
+      <c r="V56" t="n">
         <v>241</v>
       </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
         <v>0.8527687497567281</v>
       </c>
-      <c r="V56" t="n">
+      <c r="Y56" t="n">
         <v>15.99925322594204</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Z56" t="n">
         <v>0.005259847685457967</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AA56" t="n">
         <v>0.01658264351099755</v>
       </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
       <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5861,76 +6701,91 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="n">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
         <v>529</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="P57" t="n">
+      <c r="S57" t="n">
         <v>93.34073446919658</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="T57" t="n">
         <v>0.1961248954688184</v>
       </c>
-      <c r="R57" t="n">
+      <c r="U57" t="n">
         <v>0.2463816638163443</v>
       </c>
-      <c r="S57" t="n">
+      <c r="V57" t="n">
         <v>529</v>
       </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="V57" t="n">
+      <c r="Y57" t="n">
         <v>93.34073446919658</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Z57" t="n">
         <v>0.1961248954688184</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AA57" t="n">
         <v>0.2463816638163443</v>
       </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
       <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5955,76 +6810,91 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="n">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
         <v>529</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="P58" t="n">
+      <c r="S58" t="n">
         <v>759.0172445074666</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="T58" t="n">
         <v>0.2522647464126221</v>
       </c>
-      <c r="R58" t="n">
+      <c r="U58" t="n">
         <v>0.5677069240780793</v>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
         <v>529</v>
       </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="V58" t="n">
+      <c r="Y58" t="n">
         <v>759.0172445074666</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Z58" t="n">
         <v>0.2522647464126221</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AA58" t="n">
         <v>0.5677069240780793</v>
       </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
       <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6049,76 +6919,91 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="n">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
         <v>529</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="P59" t="n">
+      <c r="S59" t="n">
         <v>495.0388061151837</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="T59" t="n">
         <v>0.1629752088392055</v>
       </c>
-      <c r="R59" t="n">
+      <c r="U59" t="n">
         <v>0.2458339990601101</v>
       </c>
-      <c r="S59" t="n">
+      <c r="V59" t="n">
         <v>529</v>
       </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="V59" t="n">
+      <c r="Y59" t="n">
         <v>495.0388061151837</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Z59" t="n">
         <v>0.1629752088392055</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AA59" t="n">
         <v>0.2458339990601101</v>
       </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
       <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6143,76 +7028,91 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="n">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
         <v>529</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="P60" t="n">
+      <c r="S60" t="n">
         <v>627.1678526177893</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="T60" t="n">
         <v>0.2046958230473317</v>
       </c>
-      <c r="R60" t="n">
+      <c r="U60" t="n">
         <v>0.2967338089949421</v>
       </c>
-      <c r="S60" t="n">
+      <c r="V60" t="n">
         <v>529</v>
       </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="V60" t="n">
+      <c r="Y60" t="n">
         <v>627.1678526177893</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Z60" t="n">
         <v>0.2046958230473317</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AA60" t="n">
         <v>0.2967338089949421</v>
       </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
       <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6237,76 +7137,91 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="n">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
         <v>529</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="P61" t="n">
+      <c r="S61" t="n">
         <v>654.366711284982</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="T61" t="n">
         <v>0.2151268676848133</v>
       </c>
-      <c r="R61" t="n">
+      <c r="U61" t="n">
         <v>0.3152191137665913</v>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
         <v>529</v>
       </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
         <v>0.9307340173133271</v>
       </c>
-      <c r="V61" t="n">
+      <c r="Y61" t="n">
         <v>654.366711284982</v>
       </c>
-      <c r="W61" t="n">
+      <c r="Z61" t="n">
         <v>0.2151268676848133</v>
       </c>
-      <c r="X61" t="n">
+      <c r="AA61" t="n">
         <v>0.3152191137665913</v>
       </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
       <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6331,76 +7246,91 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>W m^-2 nm^-1</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>W m^-2</t>
         </is>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>475.9249673330567</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="n">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
         <v>542</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="P62" t="n">
+      <c r="S62" t="n">
         <v>93.23927366980772</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="T62" t="n">
         <v>0.1959117089239784</v>
       </c>
-      <c r="R62" t="n">
+      <c r="U62" t="n">
         <v>0.2469956870634438</v>
       </c>
-      <c r="S62" t="n">
+      <c r="V62" t="n">
         <v>542</v>
       </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="V62" t="n">
+      <c r="Y62" t="n">
         <v>93.23927366980772</v>
       </c>
-      <c r="W62" t="n">
+      <c r="Z62" t="n">
         <v>0.1959117089239784</v>
       </c>
-      <c r="X62" t="n">
+      <c r="AA62" t="n">
         <v>0.2469956870634438</v>
       </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
       <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6425,76 +7355,91 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>3008.812191561496</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
         <v>542</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="P63" t="n">
+      <c r="S63" t="n">
         <v>892.4717117342402</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="T63" t="n">
         <v>0.2966192819336692</v>
       </c>
-      <c r="R63" t="n">
+      <c r="U63" t="n">
         <v>0.5139172930324493</v>
       </c>
-      <c r="S63" t="n">
+      <c r="V63" t="n">
         <v>542</v>
       </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="V63" t="n">
+      <c r="Y63" t="n">
         <v>892.4717117342402</v>
       </c>
-      <c r="W63" t="n">
+      <c r="Z63" t="n">
         <v>0.2966192819336692</v>
       </c>
-      <c r="X63" t="n">
+      <c r="AA63" t="n">
         <v>0.5139172930324493</v>
       </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
       <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6519,76 +7464,91 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>3037.509874299953</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
         <v>542</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="P64" t="n">
+      <c r="S64" t="n">
         <v>586.9445946426193</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="T64" t="n">
         <v>0.1932321602009248</v>
       </c>
-      <c r="R64" t="n">
+      <c r="U64" t="n">
         <v>0.2862708878592347</v>
       </c>
-      <c r="S64" t="n">
+      <c r="V64" t="n">
         <v>542</v>
       </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="V64" t="n">
+      <c r="Y64" t="n">
         <v>586.9445946426193</v>
       </c>
-      <c r="W64" t="n">
+      <c r="Z64" t="n">
         <v>0.1932321602009248</v>
       </c>
-      <c r="X64" t="n">
+      <c r="AA64" t="n">
         <v>0.2862708878592347</v>
       </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
       <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6613,76 +7573,91 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>3063.901565166622</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
         <v>542</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="P65" t="n">
+      <c r="S65" t="n">
         <v>695.2414223443242</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="T65" t="n">
         <v>0.2269137593219368</v>
       </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
         <v>0.335858759487891</v>
       </c>
-      <c r="S65" t="n">
+      <c r="V65" t="n">
         <v>542</v>
       </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="V65" t="n">
+      <c r="Y65" t="n">
         <v>695.2414223443242</v>
       </c>
-      <c r="W65" t="n">
+      <c r="Z65" t="n">
         <v>0.2269137593219368</v>
       </c>
-      <c r="X65" t="n">
+      <c r="AA65" t="n">
         <v>0.335858759487891</v>
       </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
       <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6707,76 +7682,91 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>constant</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>absorbance proxy (user-provided signal, no Beer-Lambert)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>relative</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>relative_integral</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>3041.771203788956</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="n">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
         <v>542</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="P66" t="n">
+      <c r="S66" t="n">
         <v>736.723728619867</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="T66" t="n">
         <v>0.2422022168209671</v>
       </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
         <v>0.3614376742761461</v>
       </c>
-      <c r="S66" t="n">
+      <c r="V66" t="n">
         <v>542</v>
       </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
         <v>0.9127510920144639</v>
       </c>
-      <c r="V66" t="n">
+      <c r="Y66" t="n">
         <v>736.723728619867</v>
       </c>
-      <c r="W66" t="n">
+      <c r="Z66" t="n">
         <v>0.2422022168209671</v>
       </c>
-      <c r="X66" t="n">
+      <c r="AA66" t="n">
         <v>0.3614376742761461</v>
       </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
       <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
         <v>0</v>
       </c>
     </row>
